--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487176_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487176_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.563599999999999</v>
+        <v>8.7744</v>
       </c>
       <c r="E2" t="n">
-        <v>8.229100000000001</v>
+        <v>8.0289</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3344</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>5.989</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6445</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2657</v>
+        <v>0.0655</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3788</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.3109</v>
+        <v>7.2073</v>
       </c>
       <c r="E3" t="n">
-        <v>5.422</v>
+        <v>4.8806</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8889</v>
+        <v>2.3267</v>
       </c>
       <c r="G3" t="n">
         <v>3.8356</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2896</v>
+        <v>0.1861</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6808</v>
+        <v>0.1395</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6087</v>
+        <v>0.0466</v>
       </c>
       <c r="V3" t="n">
         <v>2.4137</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9075</v>
+        <v>5.9204</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9557</v>
+        <v>4.156</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9518</v>
+        <v>1.7644</v>
       </c>
       <c r="G4" t="n">
         <v>1.2526</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3523</v>
+        <v>0.3652</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4019</v>
+        <v>-0.2016</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7542</v>
+        <v>0.5668</v>
       </c>
       <c r="V4" t="n">
         <v>6.4257</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2728</v>
+        <v>5.0388</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6262</v>
+        <v>4.2852</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6465</v>
+        <v>0.7536</v>
       </c>
       <c r="G5" t="n">
         <v>3.727</v>
@@ -844,13 +844,13 @@
         <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3226</v>
+        <v>0.0886</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7549</v>
+        <v>0.4138</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4323</v>
+        <v>-0.3252</v>
       </c>
       <c r="V5" t="n">
         <v>-0.8999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3157</v>
+        <v>4.5299</v>
       </c>
       <c r="E6" t="n">
         <v>4.636</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3203</v>
+        <v>-0.1062</v>
       </c>
       <c r="G6" t="n">
         <v>3.8694</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8818</v>
+        <v>-0.6676</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3569</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5248</v>
+        <v>-0.3107</v>
       </c>
       <c r="V6" t="n">
         <v>0.9421</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7608</v>
+        <v>3.1147</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1571</v>
+        <v>2.4575</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6037</v>
+        <v>0.6572</v>
       </c>
       <c r="G7" t="n">
         <v>2.03</v>
@@ -1000,13 +1000,13 @@
         <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0515</v>
+        <v>0.4055</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2683</v>
+        <v>0.0321</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3199</v>
+        <v>0.3734</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3894</v>
+        <v>2.7166</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3475</v>
+        <v>1.407</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0419</v>
+        <v>1.3096</v>
       </c>
       <c r="G8" t="n">
         <v>1.4141</v>
@@ -1078,13 +1078,13 @@
         <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.3417</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0462</v>
+        <v>0.0132</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6227</v>
+        <v>-0.355</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3432</v>
+        <v>1.1359</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7968</v>
+        <v>0.4557</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5464</v>
+        <v>0.6803</v>
       </c>
       <c r="G9" t="n">
         <v>1.2843</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1342</v>
+        <v>-0.3414</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3107</v>
+        <v>-0.0304</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4449</v>
+        <v>-0.311</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. PÉREZ DE SAN ROMÁN</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4792</v>
+        <v>0.8461</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7665999999999999</v>
+        <v>-0.4218</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2875</v>
+        <v>1.2678</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2121</v>
+        <v>0.2337</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1656</v>
+        <v>1.6239</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3777</v>
+        <v>-1.3902</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6926</v>
+        <v>1.3877</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0414</v>
+        <v>1.8111</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6512</v>
+        <v>-0.4234</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4805</v>
+        <v>-1.154</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.207</v>
+        <v>-0.1872</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2735</v>
+        <v>-0.9668</v>
       </c>
       <c r="P10" t="n">
         <v>0.193</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="S10" t="n">
-        <v>0.074</v>
+        <v>0.4194</v>
       </c>
       <c r="T10" t="n">
-        <v>0.074</v>
+        <v>0.1207</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.2987</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>D. PÉREZ DE SAN ROMÁN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2434</v>
+        <v>0.5793</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2869</v>
+        <v>0.8668</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5303</v>
+        <v>-0.2875</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0473</v>
+        <v>0.2121</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5285</v>
+        <v>-0.1656</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4812</v>
+        <v>0.3777</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3742</v>
+        <v>0.6926</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5472</v>
+        <v>0.0414</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9214</v>
+        <v>0.6512</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4215</v>
+        <v>-0.4805</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9813</v>
+        <v>-0.207</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5598</v>
+        <v>-0.2735</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0271</v>
+        <v>0.1742</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0873</v>
+        <v>0.1742</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1144</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.4972</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1213</v>
+        <v>-0.3276</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0563</v>
+        <v>0.8248</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9948</v>
+        <v>0.0473</v>
       </c>
       <c r="H12" t="n">
-        <v>0.651</v>
+        <v>2.5285</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6458</v>
+        <v>-2.4812</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0747</v>
+        <v>-0.3742</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4709</v>
+        <v>1.5472</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5455</v>
+        <v>-1.9214</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9202</v>
+        <v>0.4215</v>
       </c>
       <c r="N12" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.5598</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.7371</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.7371</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="U12" t="n">
         <v>0.1801</v>
       </c>
-      <c r="O12" t="n">
-        <v>-1.1003</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.3511</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3511</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.0053</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.08989999999999999</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.08459999999999999</v>
-      </c>
       <c r="V12" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5717</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1762</v>
+        <v>0.4121</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1228</v>
+        <v>0.5219</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9466</v>
+        <v>-0.1098</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2337</v>
+        <v>-0.9948</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6239</v>
+        <v>0.651</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3902</v>
+        <v>-1.6458</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3877</v>
+        <v>-0.0747</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8111</v>
+        <v>0.4709</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4234</v>
+        <v>-0.5455</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.154</v>
+        <v>-0.9202</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1872</v>
+        <v>0.1801</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9668</v>
+        <v>-1.1003</v>
       </c>
       <c r="P13" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6028</v>
+        <v>0.3417</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5803</v>
+        <v>0.3107</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0225</v>
+        <v>0.031</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>40.47539999999999</v>
+        <v>40.77270000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>30.6486</v>
+        <v>30.9462</v>
       </c>
       <c r="F14" t="n">
-        <v>9.826400000000001</v>
+        <v>9.8264</v>
       </c>
       <c r="G14" t="n">
         <v>22.9003</v>
@@ -1525,13 +1525,13 @@
         <v>19.9328</v>
       </c>
       <c r="L14" t="n">
-        <v>9.668099999999999</v>
+        <v>9.668100000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-6.7005</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9324999999999999</v>
+        <v>0.9325</v>
       </c>
       <c r="O14" t="n">
         <v>-7.633</v>
@@ -1546,13 +1546,13 @@
         <v>19.301</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4144</v>
+        <v>1.712</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4298999999999997</v>
+        <v>0.7274</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9845999999999999</v>
+        <v>0.9844999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>6.510100000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7619</v>
+        <v>-0.0333</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0191</v>
+        <v>0.5184</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2573</v>
+        <v>-0.5517</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8468</v>
@@ -1624,13 +1624,13 @@
         <v>0.772</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7787</v>
+        <v>0.9835</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9928</v>
+        <v>0.4921</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7859</v>
+        <v>0.4914</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9421</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.175</v>
+        <v>-0.9559</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5393</v>
+        <v>0.1617</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6357</v>
+        <v>-1.1175</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3253</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6015</v>
+        <v>0.8206</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5208</v>
+        <v>0.1801</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1223</v>
+        <v>0.6405</v>
       </c>
       <c r="V16" t="n">
         <v>0.2859</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5917</v>
+        <v>-1.0371</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3022</v>
+        <v>1.4023</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8938</v>
+        <v>-2.4394</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3554</v>
@@ -1780,13 +1780,13 @@
         <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5294</v>
+        <v>0.0251</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3741</v>
+        <v>-0.2739</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1554</v>
+        <v>0.2991</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8076</v>
+        <v>-2.6084</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7925</v>
+        <v>-1.9942</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0151</v>
+        <v>-0.6142</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9987</v>
@@ -1858,13 +1858,13 @@
         <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1561</v>
+        <v>0.3553</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6009</v>
+        <v>0.3993</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4449</v>
+        <v>-0.044</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.443</v>
+        <v>-3.0873</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7155</v>
+        <v>-0.8142</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7275</v>
+        <v>-2.2731</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5538</v>
@@ -1936,13 +1936,13 @@
         <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3451</v>
+        <v>0.0106</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9227</v>
+        <v>-0.0214</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4224</v>
+        <v>0.032</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.2506</v>
+        <v>-6.8776</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2259</v>
+        <v>-1.2273</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.0248</v>
+        <v>-5.6503</v>
       </c>
       <c r="G20" t="n">
         <v>-5.2142</v>
@@ -2014,13 +2014,13 @@
         <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5149</v>
+        <v>-0.112</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1991</v>
+        <v>0.1977</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6841</v>
+        <v>-0.3097</v>
       </c>
       <c r="V20" t="n">
         <v>0.5717</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0701</v>
+        <v>-7.084</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4517</v>
+        <v>-0.2514</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.6184</v>
+        <v>-6.8326</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0855</v>
@@ -2092,13 +2092,13 @@
         <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4984</v>
+        <v>-0.5123</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7139</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2155</v>
+        <v>0.0013</v>
       </c>
       <c r="V21" t="n">
         <v>-2.784</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.831200000000001</v>
+        <v>-8.003</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4789</v>
+        <v>-3.0783</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.3523</v>
+        <v>-4.9247</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2537</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7053</v>
+        <v>-0.8771</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1752</v>
+        <v>-0.7746</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5301</v>
+        <v>-0.1025</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5561</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.0679</v>
+        <v>-9.4535</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.944</v>
+        <v>-4.5435</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.1238</v>
+        <v>-4.91</v>
       </c>
       <c r="G23" t="n">
         <v>-7.2668</v>
@@ -2248,13 +2248,13 @@
         <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3874</v>
+        <v>-0.773</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0708</v>
+        <v>-0.6702</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3166</v>
+        <v>-0.1028</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7997</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-40.4752</v>
+        <v>-39.1401</v>
       </c>
       <c r="E24" t="n">
         <v>-9.826499999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-30.6487</v>
+        <v>-29.3135</v>
       </c>
       <c r="G24" t="n">
         <v>-22.9002</v>
@@ -2326,13 +2326,13 @@
         <v>9.650399999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4144</v>
+        <v>-0.07930000000000004</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9846999999999999</v>
+        <v>-0.9844999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4298</v>
+        <v>0.9053</v>
       </c>
       <c r="V24" t="n">
         <v>-6.510199999999999</v>
